--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T09:28:26+00:00</t>
+    <t>2025-02-06T11:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T11:21:55+00:00</t>
+    <t>2025-02-06T12:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T12:00:33+00:00</t>
+    <t>2025-02-10T09:34:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T09:34:03+00:00</t>
+    <t>2025-02-10T11:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MOPEDClaimResponse#ClaimResponse</t>
+    <t>element:http://example.org/StructureDefinition/MopedLKFResponse#ClaimResponse</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/moped-ext-Beihilfenaequivalent</t>
+    <t>https://elga.moped.at/StructureDefinition/moped-ext-Beihilfenaequivalent</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -126,7 +126,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:http://example.org/StructureDefinition/MopedLKFResponse#ClaimResponse</t>
+    <t>element:https://elga.moped.at/StructureDefinition/MopedLKFResponse#ClaimResponse</t>
   </si>
   <si>
     <t>ID</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-moped-ext-Beihilfenaequivalent.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
